--- a/data/trans_orig/IP07_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59107</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52316</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65391</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>70972</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64694</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76900</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65082</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>77192</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59107</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51785</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66031</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120559</t>
+          <t>120321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139526</t>
+          <t>139407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27094</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20810</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33885</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,14%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19895</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13967</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26173</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13675</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25785</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27094</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20170</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34416</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37542</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86201</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86201</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>360728</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>345525</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>375432</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>72,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>320312</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>305056</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>334188</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>306644</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>333633</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>76,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>360728</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>346825</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>376458</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>75,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>661174</t>
+          <t>662312</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>700255</t>
+          <t>700725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>114763</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100059</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>129966</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95775</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81899</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>111031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>82454</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>109443</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,02%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>114763</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>99033</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>128666</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191324</t>
+          <t>190854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230405</t>
+          <t>229267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475491</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>475491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131462</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>123576</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>138751</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>137187</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127200</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>145363</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>127760</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>145060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>131462</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122653</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138184</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255949</t>
+          <t>256214</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279397</t>
+          <t>279184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26009</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18720</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33895</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36879</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28703</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46866</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29006</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46306</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>26009</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19287</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34818</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75588</t>
+          <t>75323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157471</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>551297</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>532649</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>568756</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>510969</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>544993</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>509734</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>544114</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>551297</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>533273</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>567664</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1053815</t>
+          <t>1054462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105065</t>
+          <t>1105437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167866</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>150407</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>186514</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>152550</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>136028</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170052</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>136907</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>171287</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>22,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167866</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>151499</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>185890</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295119</t>
+          <t>294747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346369</t>
+          <t>345722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>719163</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>719163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60035</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51983</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66505</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62028</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53966</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69012</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>54172</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69176</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>67,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60035</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52480</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66823</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112154</t>
+          <t>110702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132428</t>
+          <t>131603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25318</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18848</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33370</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30341</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23357</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23193</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38197</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,85%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25318</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18530</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32873</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65567</t>
+          <t>67019</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>366677</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>349124</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>381948</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>501</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>346309</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>332209</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>360836</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>330851</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>359755</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>76,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>366677</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>350500</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>382269</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>691876</t>
+          <t>691701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>734734</t>
+          <t>735344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124947</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109676</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142500</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104467</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89940</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>118567</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>91021</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119925</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>124947</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>109355</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>141124</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207665</t>
+          <t>207055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250523</t>
+          <t>250698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>491624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>653</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>450776</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>491624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132963</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>123305</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>142597</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>71,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>125302</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>114943</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>134796</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>116571</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>133653</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>132963</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122770</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>141618</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244482</t>
+          <t>244196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270330</t>
+          <t>271429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39265</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29631</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48923</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40724</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31230</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51083</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>32373</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>49455</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>39265</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30610</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>49458</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67924</t>
+          <t>66825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>94058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166026</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>559675</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>541469</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>580497</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>770</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>514352</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>551741</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>513145</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>553843</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>559675</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>539273</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>578663</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1063126</t>
+          <t>1065822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1120640</t>
+          <t>1120904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>189530</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168708</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>175531</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157429</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>194818</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>155327</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>196025</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>189530</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>170542</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>209932</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337735</t>
+          <t>337471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395249</t>
+          <t>392553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>749205</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>749205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56261</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50448</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61200</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47370</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41789</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51916</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41434</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51584</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56261</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49756</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60583</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95748</t>
+          <t>95590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110123</t>
+          <t>109897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12353</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7414</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18166</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12008</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7462</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17589</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17944</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12353</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8031</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18858</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>419993</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>405737</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>430620</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>415190</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>401937</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>425981</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>402426</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>426428</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>88,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>419993</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>405941</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>432412</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>818307</t>
+          <t>817767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>851401</t>
+          <t>849982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,95%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66568</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80824</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53803</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43012</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67056</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>42565</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66567</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>66568</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>54149</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>80620</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104153</t>
+          <t>105572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137247</t>
+          <t>137787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486561</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>468993</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>161182</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151403</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>147567</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139731</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>154799</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>139220</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>154164</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>86,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>161182</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>151645</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>168344</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296702</t>
+          <t>297033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319133</t>
+          <t>318483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>25667</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19074</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>23835</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16603</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31671</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17238</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32182</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>13,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25667</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18505</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35204</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>39768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61549</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>171402</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>621765</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>653037</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>592800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>623724</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>595178</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>622956</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>620838</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>653042</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1226851</t>
+          <t>1226504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1267830</t>
+          <t>1268462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>104588</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88987</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>120259</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89645</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76049</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106973</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>104595</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>104588</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>88982</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>121186</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>173335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214946</t>
+          <t>215293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40304</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33686</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45659</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37736</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44832</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44810</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>29092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>39227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>82546</t>
+          <t>75070</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68523</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>82157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16428</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11073</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23046</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16942</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9846</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30148</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34136</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>37489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>362106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>337053</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>379476</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>495</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>365430</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>350333</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>386810</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>395706</t>
+          <t>336570</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>367617</t>
+          <t>319950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>415917</t>
+          <t>350058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>698676</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>728880</t>
+          <t>672623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>789062</t>
+          <t>722687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>113572</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96202</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>138625</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>95080</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73700</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110177</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120913</t>
+          <t>95878</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100702</t>
+          <t>82390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149002</t>
+          <t>112498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>215993</t>
+          <t>209450</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>185439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248249</t>
+          <t>235503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128310</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>118046</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137547</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>110263</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>100655</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118037</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139163</t>
+          <t>109412</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127742</t>
+          <t>98086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149688</t>
+          <t>117395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>249426</t>
+          <t>237723</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234124</t>
+          <t>223356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262946</t>
+          <t>250224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40109</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50373</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39288</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31514</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48896</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,27%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>80672</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>68171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98776</t>
+          <t>95039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>503826</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>550622</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>513428</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>492434</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>537569</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>480748</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>546755</t>
+          <t>461293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>600807</t>
+          <t>497384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1093107</t>
+          <t>1011468</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1056670</t>
+          <t>980729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1126520</t>
+          <t>1039151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170109</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>150207</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>197003</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>151310</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>127169</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>172304</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>182293</t>
+          <t>148434</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161165</t>
+          <t>131798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>167889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>318543</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300190</t>
+          <t>290860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370040</t>
+          <t>349282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
